--- a/data/trans_dic/P38A-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P38A-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a</t>
+          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>49,97; 59,27</t>
+          <t>49,76; 59,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,21; 62,41</t>
+          <t>52,57; 61,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43,03; 61,3</t>
+          <t>43,87; 61,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,5; 69,03</t>
+          <t>59,38; 68,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,85; 71,96</t>
+          <t>62,13; 71,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,35; 72,07</t>
+          <t>58,34; 71,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,09; 62,93</t>
+          <t>56,1; 62,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>58,67; 65,48</t>
+          <t>58,86; 65,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>51,54; 63,58</t>
+          <t>52,06; 63,4</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,55; 84,2</t>
+          <t>78,06; 84,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71,78; 78,65</t>
+          <t>71,56; 78,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,9; 77,72</t>
+          <t>67,09; 78,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84,41; 89,89</t>
+          <t>84,34; 89,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,96; 89,41</t>
+          <t>84,2; 89,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,36; 81,69</t>
+          <t>41,64; 81,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,22; 86,35</t>
+          <t>82,18; 86,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>78,64; 83,36</t>
+          <t>78,64; 83,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,14; 77,8</t>
+          <t>51,31; 77,46</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,1; 88,66</t>
+          <t>83,2; 88,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,35; 85,25</t>
+          <t>79,36; 85,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,59; 85,31</t>
+          <t>79,09; 85,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91,76; 95,37</t>
+          <t>91,48; 95,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86,6; 91,37</t>
+          <t>86,44; 91,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,01; 89,87</t>
+          <t>84,51; 89,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,47; 91,7</t>
+          <t>88,46; 91,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83,73; 87,35</t>
+          <t>83,54; 87,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82,66; 86,84</t>
+          <t>82,72; 86,8</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,39; 94,86</t>
+          <t>90,57; 94,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86,11; 91,44</t>
+          <t>86,22; 91,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,24; 90,5</t>
+          <t>27,4; 90,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,61; 93,47</t>
+          <t>88,27; 93,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,28; 94,42</t>
+          <t>90,32; 94,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,06; 95,07</t>
+          <t>91,96; 95,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,56; 93,62</t>
+          <t>90,28; 93,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>88,86; 92,28</t>
+          <t>88,93; 92,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>45,86; 92,2</t>
+          <t>50,33; 92,24</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>92,16; 97,11</t>
+          <t>92,28; 96,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90,8; 95,47</t>
+          <t>90,99; 95,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,36; 94,6</t>
+          <t>90,44; 94,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92,76; 97,05</t>
+          <t>92,99; 96,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>92,16; 96,52</t>
+          <t>92,38; 96,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,13; 96,4</t>
+          <t>93,16; 96,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,31; 96,64</t>
+          <t>93,56; 96,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>92,27; 95,63</t>
+          <t>92,43; 95,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92,6; 95,06</t>
+          <t>92,48; 95,09</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>95,25; 98,99</t>
+          <t>95,31; 99,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95,49; 99,05</t>
+          <t>95,25; 98,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94,68; 97,9</t>
+          <t>94,93; 97,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93,27; 97,8</t>
+          <t>93,35; 97,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>96,62; 99,44</t>
+          <t>96,76; 99,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>97,6; 99,6</t>
+          <t>97,45; 99,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>95,09; 97,94</t>
+          <t>95,19; 98,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>96,78; 98,85</t>
+          <t>96,72; 98,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>96,87; 99,04</t>
+          <t>96,75; 98,95</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>94,49; 99,08</t>
+          <t>94,13; 99,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>96,22; 99,31</t>
+          <t>96,08; 99,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96,92; 99,47</t>
+          <t>96,85; 99,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97,1; 99,7</t>
+          <t>97,09; 99,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,31; 99,69</t>
+          <t>96,23; 99,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,79; 97,72</t>
+          <t>94,75; 97,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,74; 99,11</t>
+          <t>96,9; 99,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>96,89; 99,21</t>
+          <t>96,78; 99,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>96,09; 98,07</t>
+          <t>96,21; 98,14</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>83,91; 86,39</t>
+          <t>84,06; 86,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>82,19; 84,76</t>
+          <t>82,27; 84,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60,45; 84,15</t>
+          <t>60,3; 84,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88,5; 90,61</t>
+          <t>88,7; 90,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>88,79; 90,81</t>
+          <t>88,86; 90,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>81,85; 90,51</t>
+          <t>82,43; 90,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,69; 88,34</t>
+          <t>86,75; 88,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>85,96; 87,58</t>
+          <t>85,97; 87,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>73,87; 86,85</t>
+          <t>72,82; 86,61</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a</t>
+          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>224062; 265733</t>
+          <t>223117; 265900</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>213121; 254752</t>
+          <t>214564; 252479</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>172124; 245184</t>
+          <t>175491; 246879</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>253678; 294278</t>
+          <t>253144; 292590</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>247522; 283371</t>
+          <t>244687; 283153</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>182745; 225717</t>
+          <t>182707; 224925</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>490638; 550421</t>
+          <t>490710; 549735</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>470564; 525172</t>
+          <t>472017; 525774</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>367604; 453472</t>
+          <t>371317; 452169</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>537294; 575912</t>
+          <t>533936; 577171</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>422383; 462825</t>
+          <t>421093; 462966</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>283364; 329179</t>
+          <t>284137; 330346</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>514354; 547757</t>
+          <t>513957; 548172</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>472312; 502988</t>
+          <t>473672; 504432</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>221776; 417833</t>
+          <t>213011; 415904</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1063398; 1116794</t>
+          <t>1062858; 1116148</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>905173; 959529</t>
+          <t>905195; 958734</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>506226; 727429</t>
+          <t>479766; 724283</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>564336; 602060</t>
+          <t>565016; 603298</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>525760; 564844</t>
+          <t>525817; 563672</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>421528; 457530</t>
+          <t>424175; 457386</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>652303; 677942</t>
+          <t>650321; 677507</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>569584; 600969</t>
+          <t>568515; 600427</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>461135; 487535</t>
+          <t>458448; 485483</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1229622; 1274552</t>
+          <t>1229572; 1275244</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1105450; 1153300</t>
+          <t>1102913; 1156324</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>891720; 936794</t>
+          <t>892398; 936371</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>554649; 582063</t>
+          <t>555727; 581610</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>553846; 588076</t>
+          <t>554552; 587962</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>259622; 803458</t>
+          <t>243271; 804181</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>543335; 573139</t>
+          <t>541246; 573716</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>585078; 611904</t>
+          <t>585342; 613599</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>655935; 677344</t>
+          <t>655210; 677024</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1111021; 1148517</t>
+          <t>1107515; 1148097</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1147395; 1191548</t>
+          <t>1148335; 1191453</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>733947; 1475393</t>
+          <t>805451; 1476085</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>390666; 411643</t>
+          <t>391193; 411159</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>433016; 455288</t>
+          <t>433889; 456071</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>507114; 530911</t>
+          <t>507593; 530320</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>412656; 431725</t>
+          <t>413670; 431280</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>455766; 477348</t>
+          <t>456896; 477749</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>510278; 528179</t>
+          <t>510444; 528487</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>810615; 839557</t>
+          <t>812757; 838113</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>896312; 929019</t>
+          <t>897896; 928949</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1027055; 1054312</t>
+          <t>1025693; 1054727</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>291236; 302687</t>
+          <t>291435; 302696</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>319240; 331165</t>
+          <t>318450; 330435</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>348585; 360443</t>
+          <t>349498; 360229</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>327561; 343462</t>
+          <t>327843; 343361</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>364992; 375650</t>
+          <t>365534; 375729</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>593782; 605952</t>
+          <t>592853; 605679</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>624662; 643404</t>
+          <t>625333; 644384</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>689183; 703880</t>
+          <t>688762; 704293</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>945987; 967153</t>
+          <t>944836; 966295</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>234992; 246400</t>
+          <t>234077; 246386</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>246468; 254394</t>
+          <t>246116; 254404</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>274036; 281259</t>
+          <t>273862; 281290</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>377706; 387818</t>
+          <t>377677; 387821</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>385393; 398921</t>
+          <t>385079; 398926</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>403643; 416103</t>
+          <t>403460; 415780</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>616854; 631970</t>
+          <t>617865; 632122</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>635946; 651115</t>
+          <t>635172; 650748</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>680894; 694885</t>
+          <t>681721; 695387</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2855711; 2940312</t>
+          <t>2860774; 2942933</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2769411; 2856110</t>
+          <t>2772382; 2859762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2091288; 2911284</t>
+          <t>2086175; 2907628</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3136959; 3211722</t>
+          <t>3144175; 3214748</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3138530; 3209704</t>
+          <t>3141000; 3213062</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2997333; 3314381</t>
+          <t>3018496; 3318496</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6023651; 6137725</t>
+          <t>6027244; 6135003</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5934921; 6046536</t>
+          <t>5935473; 6046855</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5260639; 6184803</t>
+          <t>5186081; 6167817</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P38A-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P38A-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>55,73%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>49,76; 59,3</t>
+          <t>49,93; 59,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,57; 61,85</t>
+          <t>52,46; 62,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43,87; 61,72</t>
+          <t>41,06; 56,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,38; 68,63</t>
+          <t>59,4; 68,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,13; 71,9</t>
+          <t>62,83; 71,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,34; 71,82</t>
+          <t>57,07; 70,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,1; 62,85</t>
+          <t>56,17; 62,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>58,86; 65,56</t>
+          <t>59,16; 65,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,06; 63,4</t>
+          <t>50,3; 60,68</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,06; 84,38</t>
+          <t>78,45; 84,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71,56; 78,67</t>
+          <t>71,75; 79,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,09; 78,0</t>
+          <t>65,69; 76,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84,34; 89,96</t>
+          <t>84,74; 90,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,2; 89,67</t>
+          <t>83,82; 89,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,64; 81,31</t>
+          <t>74,46; 82,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,18; 86,3</t>
+          <t>81,94; 86,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>78,64; 83,29</t>
+          <t>78,8; 83,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51,31; 77,46</t>
+          <t>71,52; 78,27</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,2; 88,84</t>
+          <t>83,29; 88,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,36; 85,08</t>
+          <t>79,05; 85,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,09; 85,28</t>
+          <t>75,8; 82,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91,48; 95,31</t>
+          <t>91,6; 95,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86,44; 91,29</t>
+          <t>86,45; 91,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,51; 89,5</t>
+          <t>84,41; 89,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,46; 91,75</t>
+          <t>88,37; 91,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83,54; 87,58</t>
+          <t>83,6; 87,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82,72; 86,8</t>
+          <t>81,04; 85,26</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>91,24%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,57; 94,79</t>
+          <t>90,49; 94,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86,22; 91,42</t>
+          <t>86,33; 91,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,4; 90,58</t>
+          <t>87,11; 91,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,27; 93,56</t>
+          <t>88,35; 93,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,32; 94,68</t>
+          <t>90,14; 94,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,96; 95,02</t>
+          <t>91,06; 94,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,28; 93,59</t>
+          <t>90,54; 93,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>88,93; 92,27</t>
+          <t>89,07; 92,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,33; 92,24</t>
+          <t>89,67; 92,66</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>92,28; 96,99</t>
+          <t>92,25; 97,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90,99; 95,64</t>
+          <t>90,83; 95,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,44; 94,49</t>
+          <t>89,79; 94,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92,99; 96,95</t>
+          <t>92,59; 96,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>92,38; 96,6</t>
+          <t>91,91; 96,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,16; 96,46</t>
+          <t>93,78; 96,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,56; 96,47</t>
+          <t>93,28; 96,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>92,43; 95,63</t>
+          <t>92,44; 95,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92,48; 95,09</t>
+          <t>92,27; 94,89</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>95,31; 99,0</t>
+          <t>95,43; 98,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95,25; 98,83</t>
+          <t>95,52; 99,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94,93; 97,84</t>
+          <t>94,77; 97,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93,35; 97,77</t>
+          <t>93,21; 97,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>96,76; 99,46</t>
+          <t>96,66; 99,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>97,45; 99,56</t>
+          <t>96,41; 98,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>95,19; 98,09</t>
+          <t>95,1; 97,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>96,72; 98,9</t>
+          <t>96,86; 98,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>96,75; 98,95</t>
+          <t>96,17; 98,06</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>94,13; 99,08</t>
+          <t>94,48; 98,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>96,08; 99,31</t>
+          <t>95,88; 99,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96,85; 99,48</t>
+          <t>96,61; 99,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97,09; 99,7</t>
+          <t>97,04; 99,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,23; 99,69</t>
+          <t>96,11; 99,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,75; 97,64</t>
+          <t>94,42; 97,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,9; 99,13</t>
+          <t>96,94; 99,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>96,78; 99,15</t>
+          <t>96,81; 99,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>96,21; 98,14</t>
+          <t>95,9; 97,99</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>84,06; 86,47</t>
+          <t>84,02; 86,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>82,27; 84,87</t>
+          <t>82,1; 84,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60,3; 84,04</t>
+          <t>80,98; 84,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88,7; 90,69</t>
+          <t>88,57; 90,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>88,86; 90,9</t>
+          <t>88,75; 90,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>82,43; 90,63</t>
+          <t>87,33; 89,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,75; 88,3</t>
+          <t>86,67; 88,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>85,97; 87,58</t>
+          <t>85,91; 87,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>72,82; 86,61</t>
+          <t>84,7; 86,58</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>208516</t>
+          <t>198080</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>203851</t>
+          <t>231214</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>412367</t>
+          <t>429294</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>223117; 265900</t>
+          <t>223857; 267871</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>214564; 252479</t>
+          <t>214149; 254527</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>175491; 246879</t>
+          <t>167430; 229789</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>253144; 292590</t>
+          <t>253241; 294032</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>244687; 283153</t>
+          <t>247437; 283232</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>182707; 224925</t>
+          <t>206899; 254945</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>490710; 549735</t>
+          <t>491332; 550271</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>472017; 525774</t>
+          <t>474430; 527583</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>371317; 452169</t>
+          <t>387493; 467388</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>307143</t>
+          <t>340781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>354358</t>
+          <t>393600</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>661501</t>
+          <t>734380</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>533936; 577171</t>
+          <t>536591; 576459</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>421093; 462966</t>
+          <t>422200; 465488</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>284137; 330346</t>
+          <t>313284; 364029</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>513957; 548172</t>
+          <t>516365; 549163</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>473672; 504432</t>
+          <t>471565; 501767</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>213011; 415904</t>
+          <t>373110; 412125</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1062858; 1116148</t>
+          <t>1059790; 1112715</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>905195; 958734</t>
+          <t>906996; 957018</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>479766; 724283</t>
+          <t>699430; 765461</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>441169</t>
+          <t>493415</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>473953</t>
+          <t>540906</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>915123</t>
+          <t>1034321</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>565016; 603298</t>
+          <t>565581; 602962</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>525817; 563672</t>
+          <t>523739; 564354</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>424175; 457386</t>
+          <t>470571; 514026</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>650321; 677507</t>
+          <t>651157; 678211</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>568515; 600427</t>
+          <t>568607; 600914</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>458448; 485483</t>
+          <t>525154; 553800</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1229572; 1275244</t>
+          <t>1228275; 1273928</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1102913; 1156324</t>
+          <t>1103793; 1156230</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>892398; 936371</t>
+          <t>1007274; 1059820</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>574936</t>
+          <t>628926</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>667181</t>
+          <t>682315</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1242118</t>
+          <t>1311241</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>555727; 581610</t>
+          <t>555220; 582143</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>554552; 587962</t>
+          <t>555213; 588517</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>243271; 804181</t>
+          <t>610317; 643186</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>541246; 573716</t>
+          <t>541751; 572061</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>585342; 613599</t>
+          <t>584171; 611501</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>655210; 677024</t>
+          <t>670631; 692504</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1107515; 1148097</t>
+          <t>1110723; 1149650</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1148335; 1191453</t>
+          <t>1150102; 1194354</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>805451; 1476085</t>
+          <t>1288640; 1331559</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>520736</t>
+          <t>561495</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>520675</t>
+          <t>579857</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1041411</t>
+          <t>1141353</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>391193; 411159</t>
+          <t>391049; 411589</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>433889; 456071</t>
+          <t>433126; 455649</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>507593; 530320</t>
+          <t>547154; 574121</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>413670; 431280</t>
+          <t>411884; 430733</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>456896; 477749</t>
+          <t>454562; 477059</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>510444; 528487</t>
+          <t>570982; 587264</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>812757; 838113</t>
+          <t>810395; 838099</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>897896; 928949</t>
+          <t>897963; 927757</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1025693; 1054727</t>
+          <t>1124087; 1155962</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>355651</t>
+          <t>392635</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>600276</t>
+          <t>429768</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>955927</t>
+          <t>822403</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>291435; 302696</t>
+          <t>291793; 302585</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>318450; 330435</t>
+          <t>319364; 330974</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>349498; 360229</t>
+          <t>385790; 398183</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>327843; 343361</t>
+          <t>327344; 343051</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>365534; 375729</t>
+          <t>365129; 375551</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>592853; 605679</t>
+          <t>423391; 433552</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>625333; 644384</t>
+          <t>624759; 643476</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>688762; 704293</t>
+          <t>689723; 704167</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>944836; 966295</t>
+          <t>813799; 829823</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>278386</t>
+          <t>305335</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>410670</t>
+          <t>446722</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>689057</t>
+          <t>752057</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>234077; 246386</t>
+          <t>234957; 246028</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>246116; 254404</t>
+          <t>245615; 254412</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>273862; 281290</t>
+          <t>299696; 308413</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>377677; 387821</t>
+          <t>377474; 387819</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>385079; 398926</t>
+          <t>384617; 398894</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>403460; 415780</t>
+          <t>438697; 452415</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>617865; 632122</t>
+          <t>618160; 632006</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>635172; 650748</t>
+          <t>635397; 650468</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>681721; 695387</t>
+          <t>743004; 759205</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2686540</t>
+          <t>2920668</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3230964</t>
+          <t>3304382</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5917504</t>
+          <t>6225050</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2860774; 2942933</t>
+          <t>2859498; 2945380</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2772382; 2859762</t>
+          <t>2766571; 2861634</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2086175; 2907628</t>
+          <t>2860688; 2978934</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3144175; 3214748</t>
+          <t>3139531; 3211973</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3141000; 3213062</t>
+          <t>3136841; 3209728</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3018496; 3318496</t>
+          <t>3261548; 3344085</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6027244; 6135003</t>
+          <t>6022229; 6135304</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5935473; 6046855</t>
+          <t>5931871; 6042142</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5186081; 6167817</t>
+          <t>6155819; 6292662</t>
         </is>
       </c>
     </row>
